--- a/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.2 客户业务变更/2. 用户停用和恢复.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.2 客户业务变更/2. 用户停用和恢复.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="239">
   <si>
     <t>业务属性</t>
   </si>
@@ -341,9 +341,6 @@
   </si>
   <si>
     <t>自由文本，非空</t>
-  </si>
-  <si>
-    <t>NVARCHAR2</t>
   </si>
   <si>
     <t>支持中文、自由文本</t>
@@ -746,7 +743,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -808,13 +805,6 @@
       <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1375,48 +1365,51 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1426,97 +1419,94 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2543,13 +2533,13 @@
         <v>77</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>79</v>
       </c>
       <c r="R7" s="6">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>75</v>
@@ -2573,7 +2563,7 @@
         <v>83</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA7" s="7" t="s">
         <v>85</v>
@@ -2582,21 +2572,21 @@
         <v>86</v>
       </c>
       <c r="AC7" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD7" s="27" t="s">
         <v>111</v>
-      </c>
-      <c r="AD7" s="27" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:30">
       <c r="A8" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>69</v>
@@ -2611,10 +2601,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>75</v>
@@ -2635,13 +2625,13 @@
         <v>77</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="R8" s="4">
-        <v>200</v>
+      <c r="R8" s="6">
+        <v>400</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>75</v>
@@ -2665,7 +2655,7 @@
         <v>83</v>
       </c>
       <c r="Z8" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA8" s="5" t="s">
         <v>85</v>
@@ -2674,21 +2664,21 @@
         <v>86</v>
       </c>
       <c r="AC8" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD8" s="27" t="s">
         <v>111</v>
-      </c>
-      <c r="AD8" s="27" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:30">
       <c r="A9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>69</v>
@@ -2703,10 +2693,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>75</v>
@@ -2757,10 +2747,10 @@
         <v>83</v>
       </c>
       <c r="Z9" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA9" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="AA9" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="AB9" s="6" t="s">
         <v>86</v>
@@ -2774,13 +2764,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:30">
       <c r="A10" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>69</v>
@@ -2795,10 +2785,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>75</v>
@@ -2849,10 +2839,10 @@
         <v>83</v>
       </c>
       <c r="Z10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA10" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="AB10" s="4" t="s">
         <v>86</v>
@@ -2866,13 +2856,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:30">
       <c r="A11" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>69</v>
@@ -2887,10 +2877,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>75</v>
@@ -2944,7 +2934,7 @@
         <v>96</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AB11" s="6" t="s">
         <v>86</v>
@@ -2958,13 +2948,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:30">
       <c r="A12" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>69</v>
@@ -2979,10 +2969,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>75</v>
@@ -3036,7 +3026,7 @@
         <v>96</v>
       </c>
       <c r="AA12" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AB12" s="4" t="s">
         <v>86</v>
@@ -3050,13 +3040,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:30">
       <c r="A13" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>69</v>
@@ -3071,10 +3061,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>148</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>75</v>
@@ -3142,13 +3132,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:30">
       <c r="A14" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>69</v>
@@ -3163,10 +3153,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>75</v>
@@ -3234,13 +3224,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:30">
       <c r="A15" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>69</v>
@@ -3255,10 +3245,10 @@
         <v>72</v>
       </c>
       <c r="H15" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>158</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>75</v>
@@ -3291,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>80</v>
@@ -3312,7 +3302,7 @@
         <v>96</v>
       </c>
       <c r="AA15" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AB15" s="6" t="s">
         <v>86</v>
@@ -3326,13 +3316,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:30">
       <c r="A16" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>69</v>
@@ -3347,10 +3337,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>75</v>
@@ -3383,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="U16" s="4" t="s">
         <v>80</v>
@@ -3404,7 +3394,7 @@
         <v>96</v>
       </c>
       <c r="AA16" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AB16" s="4" t="s">
         <v>86</v>
@@ -3418,13 +3408,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:30">
       <c r="A17" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>69</v>
@@ -3439,10 +3429,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>75</v>
@@ -3463,13 +3453,13 @@
         <v>77</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>79</v>
       </c>
       <c r="R17" s="6">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S17" s="6" t="s">
         <v>75</v>
@@ -3493,13 +3483,13 @@
         <v>83</v>
       </c>
       <c r="Z17" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>85</v>
       </c>
       <c r="AB17" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AC17" s="25" t="s">
         <v>87</v>
@@ -3510,13 +3500,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:30">
       <c r="A18" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>69</v>
@@ -3531,7 +3521,7 @@
         <v>72</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>108</v>
@@ -3555,13 +3545,13 @@
         <v>77</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="4" t="s">
         <v>79</v>
       </c>
       <c r="R18" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S18" s="4" t="s">
         <v>75</v>
@@ -3585,7 +3575,7 @@
         <v>83</v>
       </c>
       <c r="Z18" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA18" s="5" t="s">
         <v>85</v>
@@ -3594,21 +3584,21 @@
         <v>86</v>
       </c>
       <c r="AC18" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD18" s="27" t="s">
         <v>111</v>
-      </c>
-      <c r="AD18" s="27" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:30">
       <c r="A19" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>69</v>
@@ -3623,10 +3613,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>75</v>
@@ -3680,7 +3670,7 @@
         <v>96</v>
       </c>
       <c r="AA19" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AB19" s="6" t="s">
         <v>86</v>
@@ -3694,13 +3684,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:30">
       <c r="A20" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>69</v>
@@ -3715,10 +3705,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>75</v>
@@ -3739,10 +3729,10 @@
         <v>77</v>
       </c>
       <c r="P20" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q20" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="R20" s="4">
         <v>7</v>
@@ -3769,10 +3759,10 @@
         <v>83</v>
       </c>
       <c r="Z20" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA20" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="AA20" s="5" t="s">
-        <v>191</v>
       </c>
       <c r="AB20" s="4" t="s">
         <v>86</v>
@@ -3786,13 +3776,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:30">
       <c r="A21" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>69</v>
@@ -3807,10 +3797,10 @@
         <v>72</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>75</v>
@@ -3861,30 +3851,30 @@
         <v>83</v>
       </c>
       <c r="Z21" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>85</v>
       </c>
       <c r="AB21" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AC21" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD21" s="30" t="s">
         <v>197</v>
-      </c>
-      <c r="AD21" s="30" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:30">
       <c r="A22" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>69</v>
@@ -3899,10 +3889,10 @@
         <v>72</v>
       </c>
       <c r="H22" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>75</v>
@@ -3953,30 +3943,30 @@
         <v>83</v>
       </c>
       <c r="Z22" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA22" s="5" t="s">
         <v>85</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AC22" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD22" s="30" t="s">
         <v>197</v>
-      </c>
-      <c r="AD22" s="30" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:30">
       <c r="A23" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>69</v>
@@ -3991,10 +3981,10 @@
         <v>72</v>
       </c>
       <c r="H23" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>75</v>
@@ -4048,7 +4038,7 @@
         <v>96</v>
       </c>
       <c r="AA23" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AB23" s="6" t="s">
         <v>86</v>
@@ -4062,13 +4052,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:30">
       <c r="A24" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>69</v>
@@ -4083,10 +4073,10 @@
         <v>72</v>
       </c>
       <c r="H24" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I24" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>75</v>
@@ -4107,10 +4097,10 @@
         <v>77</v>
       </c>
       <c r="P24" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q24" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="R24" s="4">
         <v>7</v>
@@ -4137,10 +4127,10 @@
         <v>83</v>
       </c>
       <c r="Z24" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA24" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="AA24" s="5" t="s">
-        <v>191</v>
       </c>
       <c r="AB24" s="4" t="s">
         <v>86</v>
@@ -4154,13 +4144,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:30">
       <c r="A25" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>69</v>
@@ -4175,10 +4165,10 @@
         <v>72</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>75</v>
@@ -4232,7 +4222,7 @@
         <v>96</v>
       </c>
       <c r="AA25" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AB25" s="6" t="s">
         <v>86</v>
@@ -4246,13 +4236,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:30">
       <c r="A26" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>69</v>
@@ -4267,10 +4257,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I26" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>223</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>75</v>
@@ -4291,10 +4281,10 @@
         <v>77</v>
       </c>
       <c r="P26" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q26" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="R26" s="4">
         <v>7</v>
@@ -4321,10 +4311,10 @@
         <v>83</v>
       </c>
       <c r="Z26" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA26" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="AA26" s="5" t="s">
-        <v>191</v>
       </c>
       <c r="AB26" s="4" t="s">
         <v>86</v>
@@ -4338,13 +4328,13 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:30">
       <c r="A27" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>69</v>
@@ -4359,10 +4349,10 @@
         <v>72</v>
       </c>
       <c r="H27" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>228</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>75</v>
@@ -4416,10 +4406,10 @@
         <v>85</v>
       </c>
       <c r="AA27" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AB27" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AC27" s="25" t="s">
         <v>87</v>
@@ -4430,13 +4420,13 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:30">
       <c r="A28" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>69</v>
@@ -4451,10 +4441,10 @@
         <v>72</v>
       </c>
       <c r="H28" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>75</v>
@@ -4508,10 +4498,10 @@
         <v>96</v>
       </c>
       <c r="AA28" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AB28" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AC28" s="23" t="s">
         <v>87</v>
@@ -4522,13 +4512,13 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:30">
       <c r="A29" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>69</v>
@@ -4543,10 +4533,10 @@
         <v>72</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>75</v>
@@ -4567,7 +4557,7 @@
         <v>77</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q29" s="6" t="s">
         <v>79</v>
@@ -4597,13 +4587,13 @@
         <v>83</v>
       </c>
       <c r="Z29" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>85</v>
       </c>
       <c r="AB29" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AC29" s="25" t="s">
         <v>87</v>
